--- a/artfynd/A 1521-2026 artfynd.xlsx
+++ b/artfynd/A 1521-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112192240</v>
+        <v>112192245</v>
       </c>
       <c r="B2" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Alfhem SO, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420019</v>
+        <v>420022</v>
       </c>
       <c r="R2" t="n">
-        <v>6464807</v>
+        <v>6464839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,12 +765,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Naturbetesmark / Hagmark</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,6 +791,418 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91922057</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korpatorp - N6830 -. 1996, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>420036</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6464648</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lövsumpskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112192240</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alfhem SO, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420019</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6464807</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Naturbetesmark / Hagmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112532162</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Litatorp, kring, Bolum 3:8, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>420249</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6464785</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Planterad granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112192057</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alfhem SO, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>420097</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6464683</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
